--- a/codespace/results/ch3_fw1_nodewise_anova_report.xlsx
+++ b/codespace/results/ch3_fw1_nodewise_anova_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5291563474313765</v>
+        <v>0.05094527470459983</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3301317575109</v>
+        <v>0.498881880142244</v>
       </c>
       <c r="G2" t="n">
-        <v>108.2513293804306</v>
+        <v>105.4030844506785</v>
       </c>
       <c r="H2" t="n">
-        <v>4.664421062459466e-15</v>
+        <v>7.820358459558719e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>7.463073699935145e-14</v>
+        <v>1.251257353529395e-13</v>
       </c>
     </row>
     <row r="3">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.943652872973218</v>
+        <v>0.5800973294733582</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9963675902341</v>
+        <v>0.280448479443627</v>
       </c>
       <c r="G3" t="n">
-        <v>32.0208080814044</v>
+        <v>35.24473178032349</v>
       </c>
       <c r="H3" t="n">
-        <v>4.52851117671347e-07</v>
+        <v>1.566805403626827e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.962228316546e-06</v>
+        <v>1.253444322901461e-06</v>
       </c>
     </row>
     <row r="4">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.333435160226787</v>
+        <v>0.648616361684609</v>
       </c>
       <c r="F4" t="n">
-        <v>3.615908327524772</v>
+        <v>0.3789246037834708</v>
       </c>
       <c r="G4" t="n">
-        <v>31.41421025482011</v>
+        <v>26.8365678586406</v>
       </c>
       <c r="H4" t="n">
-        <v>5.55417809352375e-07</v>
+        <v>2.722791527455261e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.962228316546e-06</v>
+        <v>1.452155481309472e-05</v>
       </c>
     </row>
     <row r="5">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2133630212220246</v>
+        <v>0.02146305872368705</v>
       </c>
       <c r="F5" t="n">
-        <v>1.097710740948305</v>
+        <v>0.105977822909699</v>
       </c>
       <c r="G5" t="n">
-        <v>10.27622394790222</v>
+        <v>9.817734604024452</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002160800263745101</v>
+        <v>0.002673172819796543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008643201054980404</v>
+        <v>0.01069269127918617</v>
       </c>
     </row>
     <row r="6">
@@ -615,143 +615,143 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2593626709041504</v>
+        <v>0.02638922421935783</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8139623271292331</v>
+        <v>0.07649900629609974</v>
       </c>
       <c r="G6" t="n">
-        <v>6.484534563356712</v>
+        <v>6.08574059311766</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0134660472961281</v>
+        <v>0.01649998330237901</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04309135134760991</v>
+        <v>0.04422877271018816</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.02287249063246043</v>
       </c>
       <c r="F7" t="n">
-        <v>4.948722008583886</v>
+        <v>0.1049659086189728</v>
       </c>
       <c r="G7" t="n">
-        <v>60.91663251547694</v>
+        <v>6.075623526518958</v>
       </c>
       <c r="H7" t="n">
-        <v>1.823236541525022e-06</v>
+        <v>0.01658578976632056</v>
       </c>
       <c r="I7" t="n">
-        <v>2.917178466440036e-05</v>
+        <v>0.04422877271018816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.759436655131692</v>
+        <v>0.1963190913026241</v>
       </c>
       <c r="F8" t="n">
-        <v>4.023975709295212</v>
+        <v>0.3236126745715026</v>
       </c>
       <c r="G8" t="n">
-        <v>12.39077511434253</v>
+        <v>5.705166396350677</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003397110451638886</v>
+        <v>0.0200780240535277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02717688361311109</v>
+        <v>0.04589262640806332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.726425085253114</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5.889861062285988</v>
+        <v>0.5701507201625647</v>
       </c>
       <c r="G9" t="n">
-        <v>58.80986922198809</v>
+        <v>19.83438266099967</v>
       </c>
       <c r="H9" t="n">
-        <v>1.211777399080524e-09</v>
+        <v>0.0005456354046853646</v>
       </c>
       <c r="I9" t="n">
-        <v>1.938843838528839e-08</v>
+        <v>0.004453329621646888</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9608480451605085</v>
+        <v>0.8913410460724419</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1334389578463389</v>
+        <v>0.2425086214999399</v>
       </c>
       <c r="G10" t="n">
-        <v>10.02354470480702</v>
+        <v>19.74161554447949</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002805454767848111</v>
+        <v>0.000556666202705861</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01701977404906881</v>
+        <v>0.004453329621646888</v>
       </c>
     </row>
     <row r="11">
@@ -766,23 +766,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.449939947798884</v>
+        <v>0.5155538613821421</v>
       </c>
       <c r="F11" t="n">
-        <v>4.479556387716356</v>
+        <v>0.7705903202952037</v>
       </c>
       <c r="G11" t="n">
-        <v>9.232801562615812</v>
+        <v>61.14840310937722</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003990436676409866</v>
+        <v>7.331582145657771e-10</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01701977404906881</v>
+        <v>1.173053143305243e-08</v>
       </c>
     </row>
     <row r="12">
@@ -797,23 +797,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9229574874715225</v>
+        <v>0.6726529375015807</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1152023447535444</v>
+        <v>0.4952546887808211</v>
       </c>
       <c r="G12" t="n">
-        <v>8.789278191392921</v>
+        <v>12.99944165651593</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004878174666049756</v>
+        <v>0.000790423132108219</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01701977404906881</v>
+        <v>0.006323385056865752</v>
       </c>
     </row>
     <row r="13">
@@ -828,23 +828,85 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Dreissena</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.09095275804032427</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.01427174831351908</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9.339634455269021</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.003803313352045887</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.02028433787757806</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Amphipoda</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>1.02772258345535</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1513051168347085</v>
-      </c>
-      <c r="G13" t="n">
-        <v>8.600028765766606</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.005318679390334004</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.01701977404906881</v>
+      <c r="E14" t="n">
+        <v>0.09440096709446912</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.01421430773929202</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.596656831948081</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.005326900458632883</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.02110919445790493</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Caenis</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.08722635640306997</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01297278110486429</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.132986289313026</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.00659662326809529</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.02110919445790493</v>
       </c>
     </row>
   </sheetData>

--- a/codespace/results/ch3_fw1_nodewise_anova_report.xlsx
+++ b/codespace/results/ch3_fw1_nodewise_anova_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.05094527470459983</v>
+        <v>0.5132971171730633</v>
       </c>
       <c r="F2" t="n">
-        <v>0.498881880142244</v>
+        <v>0.05277153744730053</v>
       </c>
       <c r="G2" t="n">
-        <v>105.4030844506785</v>
+        <v>98.15049390206244</v>
       </c>
       <c r="H2" t="n">
-        <v>7.820358459558719e-15</v>
+        <v>3.040045850117402e-14</v>
       </c>
       <c r="I2" t="n">
-        <v>1.251257353529395e-13</v>
+        <v>4.864073360187843e-13</v>
       </c>
     </row>
     <row r="3">
@@ -511,30 +511,30 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5800973294733582</v>
+        <v>0.3383174536994699</v>
       </c>
       <c r="F3" t="n">
-        <v>0.280448479443627</v>
+        <v>0.6577411506626348</v>
       </c>
       <c r="G3" t="n">
-        <v>35.24473178032349</v>
+        <v>37.59882590183587</v>
       </c>
       <c r="H3" t="n">
-        <v>1.566805403626827e-07</v>
+        <v>7.39321515236071e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.253444322901461e-06</v>
+        <v>5.914572121888568e-07</v>
       </c>
     </row>
     <row r="4">
@@ -542,30 +542,30 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.648616361684609</v>
+        <v>0.2858176758350884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3789246037834708</v>
+        <v>0.5606764031344413</v>
       </c>
       <c r="G4" t="n">
-        <v>26.8365678586406</v>
+        <v>23.74058001952108</v>
       </c>
       <c r="H4" t="n">
-        <v>2.722791527455261e-06</v>
+        <v>8.414118406588319e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.452155481309472e-05</v>
+        <v>4.487529816847103e-05</v>
       </c>
     </row>
     <row r="5">
@@ -573,10 +573,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.02146305872368705</v>
+        <v>0.1211175118967988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.105977822909699</v>
+        <v>0.02291269773712931</v>
       </c>
       <c r="G5" t="n">
-        <v>9.817734604024452</v>
+        <v>12.51437370010309</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002673172819796543</v>
+        <v>0.000786176937088444</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01069269127918617</v>
+        <v>0.003144707748353776</v>
       </c>
     </row>
     <row r="6">
@@ -604,30 +604,30 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.02638922421935783</v>
+        <v>0.1486375519359927</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07649900629609974</v>
+        <v>0.04273892531071249</v>
       </c>
       <c r="G6" t="n">
-        <v>6.08574059311766</v>
+        <v>8.267738705141616</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01649998330237901</v>
+        <v>0.005577482603201625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04422877271018816</v>
+        <v>0.01565528526095105</v>
       </c>
     </row>
     <row r="7">
@@ -635,10 +635,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.02287249063246043</v>
+        <v>0.1199610384216832</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1049659086189728</v>
+        <v>0.02191947018944124</v>
       </c>
       <c r="G7" t="n">
-        <v>6.075623526518958</v>
+        <v>8.161799333717237</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01658578976632056</v>
+        <v>0.005870731972856644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04422877271018816</v>
+        <v>0.01565528526095105</v>
       </c>
     </row>
     <row r="8">
@@ -666,30 +666,30 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.1963190913026241</v>
+        <v>0.08742743576697112</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3236126745715026</v>
+        <v>0.02925137495982675</v>
       </c>
       <c r="G8" t="n">
-        <v>5.705166396350677</v>
+        <v>6.610164637930259</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0200780240535277</v>
+        <v>0.01263739327591361</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04589262640806332</v>
+        <v>0.0288854703449454</v>
       </c>
     </row>
     <row r="9">
@@ -697,30 +697,30 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.6937024172504632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5701507201625647</v>
+        <v>0.374439983372011</v>
       </c>
       <c r="G9" t="n">
-        <v>19.83438266099967</v>
+        <v>83.40028302465086</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005456354046853646</v>
+        <v>6.724256986397827e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004453329621646888</v>
+        <v>1.075881117823652e-10</v>
       </c>
     </row>
     <row r="10">
@@ -728,30 +728,30 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8913410460724419</v>
+        <v>0.562217492641975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2425086214999399</v>
+        <v>0.7914742718915587</v>
       </c>
       <c r="G10" t="n">
-        <v>19.74161554447949</v>
+        <v>39.04155622916043</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000556666202705861</v>
+        <v>1.227631416807537e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004453329621646888</v>
+        <v>9.821051334460295e-07</v>
       </c>
     </row>
     <row r="11">
@@ -759,30 +759,30 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5155538613821421</v>
+        <v>0.8913410460724419</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7705903202952037</v>
+        <v>0.1925621659239009</v>
       </c>
       <c r="G11" t="n">
-        <v>61.14840310937722</v>
+        <v>33.59399957399777</v>
       </c>
       <c r="H11" t="n">
-        <v>7.331582145657771e-10</v>
+        <v>8.52600014944301e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>1.173053143305243e-08</v>
+        <v>0.001364160023910882</v>
       </c>
     </row>
     <row r="12">
@@ -790,123 +790,30 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6726529375015807</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4952546887808211</v>
+        <v>0.5988466367019072</v>
       </c>
       <c r="G12" t="n">
-        <v>12.99944165651593</v>
+        <v>22.63686137673203</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000790423132108219</v>
+        <v>0.0004658541283439784</v>
       </c>
       <c r="I12" t="n">
-        <v>0.006323385056865752</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>22</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Dreissena</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.09095275804032427</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.01427174831351908</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.339634455269021</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.003803313352045887</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.02028433787757806</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" t="n">
-        <v>22</v>
-      </c>
-      <c r="C14" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Amphipoda</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.09440096709446912</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.01421430773929202</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8.596656831948081</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.005326900458632883</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.02110919445790493</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="n">
-        <v>22</v>
-      </c>
-      <c r="C15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Caenis</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.08722635640306997</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.01297278110486429</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8.132986289313026</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.00659662326809529</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.02110919445790493</v>
+        <v>0.003726833026751827</v>
       </c>
     </row>
   </sheetData>
